--- a/ah/mladina/Mladinska_selekcija_šenčur-potrjeni.xlsx
+++ b/ah/mladina/Mladinska_selekcija_šenčur-potrjeni.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\github\lzs\ah\mladina\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavlin\github\lzs\ah\mladina\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328980E4-A536-44FF-9BF5-4843F571D1D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB459BC4-A119-4934-B0EF-0892B9AEDDF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11652" xr2:uid="{E82BFDB3-015E-4898-959C-79749AB7621C}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="104">
   <si>
     <t>LK Šenčur</t>
   </si>
@@ -1848,7 +1848,9 @@
       <c r="F57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G57" s="2"/>
+      <c r="G57" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
